--- a/artfynd/A 1883-2024 artfynd.xlsx
+++ b/artfynd/A 1883-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121350440</v>
+        <v>121350445</v>
       </c>
       <c r="B2" t="n">
-        <v>97988</v>
+        <v>97998</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>606989</v>
+        <v>606512</v>
       </c>
       <c r="R2" t="n">
-        <v>6753742</v>
+        <v>6753749</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -790,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121350443</v>
+        <v>121350193</v>
       </c>
       <c r="B3" t="n">
-        <v>97988</v>
+        <v>56563</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -806,21 +806,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219790</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -828,9 +828,14 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>stationär</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -839,10 +844,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>606910</v>
+        <v>606479</v>
       </c>
       <c r="R3" t="n">
-        <v>6753715</v>
+        <v>6753729</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -905,10 +910,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121350166</v>
+        <v>121350441</v>
       </c>
       <c r="B4" t="n">
-        <v>58177</v>
+        <v>97998</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -921,21 +926,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>208245</v>
+        <v>219790</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -943,9 +948,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>adult</t>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -954,10 +959,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>606558</v>
+        <v>606974</v>
       </c>
       <c r="R4" t="n">
-        <v>6753679</v>
+        <v>6753758</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1020,10 +1025,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121350193</v>
+        <v>121350304</v>
       </c>
       <c r="B5" t="n">
-        <v>56560</v>
+        <v>97035</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1036,36 +1041,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>stationär</t>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1074,10 +1074,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>606479</v>
+        <v>606420</v>
       </c>
       <c r="R5" t="n">
-        <v>6753729</v>
+        <v>6753687</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1140,10 +1140,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121350304</v>
+        <v>121350443</v>
       </c>
       <c r="B6" t="n">
-        <v>97025</v>
+        <v>97998</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1156,31 +1156,31 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221945</v>
+        <v>219790</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1189,10 +1189,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>606420</v>
+        <v>606910</v>
       </c>
       <c r="R6" t="n">
-        <v>6753687</v>
+        <v>6753715</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1255,10 +1255,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121350445</v>
+        <v>121350447</v>
       </c>
       <c r="B7" t="n">
-        <v>97988</v>
+        <v>97998</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1304,10 +1304,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>606512</v>
+        <v>606565</v>
       </c>
       <c r="R7" t="n">
-        <v>6753749</v>
+        <v>6753689</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1370,10 +1370,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121350447</v>
+        <v>121350449</v>
       </c>
       <c r="B8" t="n">
-        <v>97988</v>
+        <v>97998</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1419,10 +1419,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>606565</v>
+        <v>606549</v>
       </c>
       <c r="R8" t="n">
-        <v>6753689</v>
+        <v>6753577</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1485,10 +1485,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121350449</v>
+        <v>121350440</v>
       </c>
       <c r="B9" t="n">
-        <v>97988</v>
+        <v>97998</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1534,10 +1534,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>606549</v>
+        <v>606989</v>
       </c>
       <c r="R9" t="n">
-        <v>6753577</v>
+        <v>6753742</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1600,10 +1600,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121350441</v>
+        <v>121350302</v>
       </c>
       <c r="B10" t="n">
-        <v>97988</v>
+        <v>97035</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1616,31 +1616,31 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219790</v>
+        <v>221945</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1649,10 +1649,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>606974</v>
+        <v>606981</v>
       </c>
       <c r="R10" t="n">
-        <v>6753758</v>
+        <v>6753750</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1715,10 +1715,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121350302</v>
+        <v>121350166</v>
       </c>
       <c r="B11" t="n">
-        <v>97025</v>
+        <v>58180</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1731,31 +1731,31 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221945</v>
+        <v>208245</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>dm²</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>adult</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1764,10 +1764,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>606981</v>
+        <v>606558</v>
       </c>
       <c r="R11" t="n">
-        <v>6753750</v>
+        <v>6753679</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 1883-2024 artfynd.xlsx
+++ b/artfynd/A 1883-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121350445</v>
+        <v>121350447</v>
       </c>
       <c r="B2" t="n">
         <v>97998</v>
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>606512</v>
+        <v>606565</v>
       </c>
       <c r="R2" t="n">
-        <v>6753749</v>
+        <v>6753689</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -910,7 +910,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121350441</v>
+        <v>121350443</v>
       </c>
       <c r="B4" t="n">
         <v>97998</v>
@@ -959,10 +959,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>606974</v>
+        <v>606910</v>
       </c>
       <c r="R4" t="n">
-        <v>6753758</v>
+        <v>6753715</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1140,7 +1140,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121350443</v>
+        <v>121350449</v>
       </c>
       <c r="B6" t="n">
         <v>97998</v>
@@ -1189,10 +1189,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>606910</v>
+        <v>606549</v>
       </c>
       <c r="R6" t="n">
-        <v>6753715</v>
+        <v>6753577</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1255,7 +1255,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121350447</v>
+        <v>121350445</v>
       </c>
       <c r="B7" t="n">
         <v>97998</v>
@@ -1304,10 +1304,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>606565</v>
+        <v>606512</v>
       </c>
       <c r="R7" t="n">
-        <v>6753689</v>
+        <v>6753749</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1370,10 +1370,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121350449</v>
+        <v>121350302</v>
       </c>
       <c r="B8" t="n">
-        <v>97998</v>
+        <v>97035</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1386,31 +1386,31 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219790</v>
+        <v>221945</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1419,10 +1419,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>606549</v>
+        <v>606981</v>
       </c>
       <c r="R8" t="n">
-        <v>6753577</v>
+        <v>6753750</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1600,10 +1600,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121350302</v>
+        <v>121350441</v>
       </c>
       <c r="B10" t="n">
-        <v>97035</v>
+        <v>97998</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1616,31 +1616,31 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221945</v>
+        <v>219790</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1649,10 +1649,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>606981</v>
+        <v>606974</v>
       </c>
       <c r="R10" t="n">
-        <v>6753750</v>
+        <v>6753758</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>

--- a/artfynd/A 1883-2024 artfynd.xlsx
+++ b/artfynd/A 1883-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121350447</v>
+        <v>121350193</v>
       </c>
       <c r="B2" t="n">
-        <v>97998</v>
+        <v>56563</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219790</v>
+        <v>100138</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -713,9 +713,14 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>stationär</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,10 +729,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>606565</v>
+        <v>606479</v>
       </c>
       <c r="R2" t="n">
-        <v>6753689</v>
+        <v>6753729</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -790,10 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121350193</v>
+        <v>121350441</v>
       </c>
       <c r="B3" t="n">
-        <v>56563</v>
+        <v>98011</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -806,21 +811,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>219790</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -828,14 +833,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>stationär</t>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -844,10 +844,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>606479</v>
+        <v>606974</v>
       </c>
       <c r="R3" t="n">
-        <v>6753729</v>
+        <v>6753758</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -913,7 +913,7 @@
         <v>121350443</v>
       </c>
       <c r="B4" t="n">
-        <v>97998</v>
+        <v>98011</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1025,10 +1025,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121350304</v>
+        <v>121350445</v>
       </c>
       <c r="B5" t="n">
-        <v>97035</v>
+        <v>98011</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1041,31 +1041,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>219790</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1074,10 +1074,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>606420</v>
+        <v>606512</v>
       </c>
       <c r="R5" t="n">
-        <v>6753687</v>
+        <v>6753749</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1140,10 +1140,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121350449</v>
+        <v>121350302</v>
       </c>
       <c r="B6" t="n">
-        <v>97998</v>
+        <v>97048</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1156,31 +1156,31 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219790</v>
+        <v>221945</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1189,10 +1189,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>606549</v>
+        <v>606981</v>
       </c>
       <c r="R6" t="n">
-        <v>6753577</v>
+        <v>6753750</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1255,10 +1255,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121350445</v>
+        <v>121350166</v>
       </c>
       <c r="B7" t="n">
-        <v>97998</v>
+        <v>58180</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1271,21 +1271,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219790</v>
+        <v>208245</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1293,9 +1293,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>adult</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1304,10 +1304,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>606512</v>
+        <v>606558</v>
       </c>
       <c r="R7" t="n">
-        <v>6753749</v>
+        <v>6753679</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1370,10 +1370,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121350302</v>
+        <v>121350440</v>
       </c>
       <c r="B8" t="n">
-        <v>97035</v>
+        <v>98011</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1386,31 +1386,31 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221945</v>
+        <v>219790</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1419,10 +1419,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>606981</v>
+        <v>606989</v>
       </c>
       <c r="R8" t="n">
-        <v>6753750</v>
+        <v>6753742</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1485,10 +1485,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121350440</v>
+        <v>121350304</v>
       </c>
       <c r="B9" t="n">
-        <v>97998</v>
+        <v>97048</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1501,31 +1501,31 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219790</v>
+        <v>221945</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1534,10 +1534,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>606989</v>
+        <v>606420</v>
       </c>
       <c r="R9" t="n">
-        <v>6753742</v>
+        <v>6753687</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1600,10 +1600,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121350441</v>
+        <v>121350447</v>
       </c>
       <c r="B10" t="n">
-        <v>97998</v>
+        <v>98011</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1649,10 +1649,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>606974</v>
+        <v>606565</v>
       </c>
       <c r="R10" t="n">
-        <v>6753758</v>
+        <v>6753689</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1715,10 +1715,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121350166</v>
+        <v>121350449</v>
       </c>
       <c r="B11" t="n">
-        <v>58180</v>
+        <v>98011</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1731,21 +1731,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>208245</v>
+        <v>219790</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1753,9 +1753,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>adult</t>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1764,10 +1764,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>606558</v>
+        <v>606549</v>
       </c>
       <c r="R11" t="n">
-        <v>6753679</v>
+        <v>6753577</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 1883-2024 artfynd.xlsx
+++ b/artfynd/A 1883-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121350193</v>
+        <v>121350166</v>
       </c>
       <c r="B2" t="n">
-        <v>56563</v>
+        <v>58180</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>208245</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -713,14 +713,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>stationär</t>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>adult</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -729,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>606479</v>
+        <v>606558</v>
       </c>
       <c r="R2" t="n">
-        <v>6753729</v>
+        <v>6753679</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -795,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121350441</v>
+        <v>121350447</v>
       </c>
       <c r="B3" t="n">
-        <v>98011</v>
+        <v>98012</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -844,10 +839,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>606974</v>
+        <v>606565</v>
       </c>
       <c r="R3" t="n">
-        <v>6753758</v>
+        <v>6753689</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -913,7 +908,7 @@
         <v>121350443</v>
       </c>
       <c r="B4" t="n">
-        <v>98011</v>
+        <v>98012</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1025,10 +1020,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121350445</v>
+        <v>121350449</v>
       </c>
       <c r="B5" t="n">
-        <v>98011</v>
+        <v>98012</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1074,10 +1069,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>606512</v>
+        <v>606549</v>
       </c>
       <c r="R5" t="n">
-        <v>6753749</v>
+        <v>6753577</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1140,10 +1135,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121350302</v>
+        <v>121350304</v>
       </c>
       <c r="B6" t="n">
-        <v>97048</v>
+        <v>97049</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1175,7 +1170,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1189,10 +1184,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>606981</v>
+        <v>606420</v>
       </c>
       <c r="R6" t="n">
-        <v>6753750</v>
+        <v>6753687</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1255,10 +1250,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121350166</v>
+        <v>121350445</v>
       </c>
       <c r="B7" t="n">
-        <v>58180</v>
+        <v>98012</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1271,21 +1266,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>208245</v>
+        <v>219790</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1293,9 +1288,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>adult</t>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1304,10 +1299,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>606558</v>
+        <v>606512</v>
       </c>
       <c r="R7" t="n">
-        <v>6753679</v>
+        <v>6753749</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1370,10 +1365,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121350440</v>
+        <v>121350302</v>
       </c>
       <c r="B8" t="n">
-        <v>98011</v>
+        <v>97049</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1386,31 +1381,31 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219790</v>
+        <v>221945</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1419,10 +1414,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>606989</v>
+        <v>606981</v>
       </c>
       <c r="R8" t="n">
-        <v>6753742</v>
+        <v>6753750</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1485,10 +1480,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121350304</v>
+        <v>121350440</v>
       </c>
       <c r="B9" t="n">
-        <v>97048</v>
+        <v>98012</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1501,31 +1496,31 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221945</v>
+        <v>219790</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1534,10 +1529,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>606420</v>
+        <v>606989</v>
       </c>
       <c r="R9" t="n">
-        <v>6753687</v>
+        <v>6753742</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1600,10 +1595,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121350447</v>
+        <v>121350441</v>
       </c>
       <c r="B10" t="n">
-        <v>98011</v>
+        <v>98012</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1649,10 +1644,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>606565</v>
+        <v>606974</v>
       </c>
       <c r="R10" t="n">
-        <v>6753689</v>
+        <v>6753758</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1715,10 +1710,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121350449</v>
+        <v>121350193</v>
       </c>
       <c r="B11" t="n">
-        <v>98011</v>
+        <v>56563</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1731,21 +1726,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219790</v>
+        <v>100138</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1753,9 +1748,14 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>stationär</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1764,10 +1764,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>606549</v>
+        <v>606479</v>
       </c>
       <c r="R11" t="n">
-        <v>6753577</v>
+        <v>6753729</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 1883-2024 artfynd.xlsx
+++ b/artfynd/A 1883-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121350166</v>
       </c>
       <c r="B2" t="n">
-        <v>58180</v>
+        <v>58183</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -790,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121350447</v>
+        <v>121350193</v>
       </c>
       <c r="B3" t="n">
-        <v>98012</v>
+        <v>56566</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -806,21 +806,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219790</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -828,9 +828,14 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>stationär</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -839,10 +844,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>606565</v>
+        <v>606479</v>
       </c>
       <c r="R3" t="n">
-        <v>6753689</v>
+        <v>6753729</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -905,10 +910,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121350443</v>
+        <v>121350445</v>
       </c>
       <c r="B4" t="n">
-        <v>98012</v>
+        <v>98015</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -954,10 +959,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>606910</v>
+        <v>606512</v>
       </c>
       <c r="R4" t="n">
-        <v>6753715</v>
+        <v>6753749</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1020,10 +1025,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121350449</v>
+        <v>121350304</v>
       </c>
       <c r="B5" t="n">
-        <v>98012</v>
+        <v>97052</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1036,31 +1041,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219790</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1069,10 +1074,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>606549</v>
+        <v>606420</v>
       </c>
       <c r="R5" t="n">
-        <v>6753577</v>
+        <v>6753687</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1135,10 +1140,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121350304</v>
+        <v>121350443</v>
       </c>
       <c r="B6" t="n">
-        <v>97049</v>
+        <v>98015</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1151,31 +1156,31 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221945</v>
+        <v>219790</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1184,10 +1189,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>606420</v>
+        <v>606910</v>
       </c>
       <c r="R6" t="n">
-        <v>6753687</v>
+        <v>6753715</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1250,10 +1255,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121350445</v>
+        <v>121350440</v>
       </c>
       <c r="B7" t="n">
-        <v>98012</v>
+        <v>98015</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1299,10 +1304,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>606512</v>
+        <v>606989</v>
       </c>
       <c r="R7" t="n">
-        <v>6753749</v>
+        <v>6753742</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1365,10 +1370,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121350302</v>
+        <v>121350447</v>
       </c>
       <c r="B8" t="n">
-        <v>97049</v>
+        <v>98015</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1381,31 +1386,31 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221945</v>
+        <v>219790</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1414,10 +1419,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>606981</v>
+        <v>606565</v>
       </c>
       <c r="R8" t="n">
-        <v>6753750</v>
+        <v>6753689</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1480,10 +1485,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121350440</v>
+        <v>121350449</v>
       </c>
       <c r="B9" t="n">
-        <v>98012</v>
+        <v>98015</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1529,10 +1534,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>606989</v>
+        <v>606549</v>
       </c>
       <c r="R9" t="n">
-        <v>6753742</v>
+        <v>6753577</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1598,7 +1603,7 @@
         <v>121350441</v>
       </c>
       <c r="B10" t="n">
-        <v>98012</v>
+        <v>98015</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1710,10 +1715,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121350193</v>
+        <v>121350302</v>
       </c>
       <c r="B11" t="n">
-        <v>56563</v>
+        <v>97052</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1726,36 +1731,31 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100138</v>
+        <v>221945</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>stationär</t>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1764,10 +1764,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>606479</v>
+        <v>606981</v>
       </c>
       <c r="R11" t="n">
-        <v>6753729</v>
+        <v>6753750</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 1883-2024 artfynd.xlsx
+++ b/artfynd/A 1883-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121350166</v>
+        <v>121350447</v>
       </c>
       <c r="B2" t="n">
-        <v>58183</v>
+        <v>98015</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>208245</v>
+        <v>219790</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -713,9 +713,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>adult</t>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>606558</v>
+        <v>606565</v>
       </c>
       <c r="R2" t="n">
-        <v>6753679</v>
+        <v>6753689</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -790,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121350193</v>
+        <v>121350166</v>
       </c>
       <c r="B3" t="n">
-        <v>56566</v>
+        <v>58183</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -806,21 +806,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>208245</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -828,14 +828,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>stationär</t>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>adult</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -844,10 +839,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>606479</v>
+        <v>606558</v>
       </c>
       <c r="R3" t="n">
-        <v>6753729</v>
+        <v>6753679</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -910,10 +905,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121350445</v>
+        <v>121350193</v>
       </c>
       <c r="B4" t="n">
-        <v>98015</v>
+        <v>56566</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -926,21 +921,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219790</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -948,9 +943,14 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>stationär</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -959,10 +959,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>606512</v>
+        <v>606479</v>
       </c>
       <c r="R4" t="n">
-        <v>6753749</v>
+        <v>6753729</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1025,7 +1025,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121350304</v>
+        <v>121350302</v>
       </c>
       <c r="B5" t="n">
         <v>97052</v>
@@ -1060,7 +1060,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1074,10 +1074,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>606420</v>
+        <v>606981</v>
       </c>
       <c r="R5" t="n">
-        <v>6753687</v>
+        <v>6753750</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1140,7 +1140,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121350443</v>
+        <v>121350449</v>
       </c>
       <c r="B6" t="n">
         <v>98015</v>
@@ -1189,10 +1189,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>606910</v>
+        <v>606549</v>
       </c>
       <c r="R6" t="n">
-        <v>6753715</v>
+        <v>6753577</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1255,7 +1255,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121350440</v>
+        <v>121350445</v>
       </c>
       <c r="B7" t="n">
         <v>98015</v>
@@ -1304,10 +1304,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>606989</v>
+        <v>606512</v>
       </c>
       <c r="R7" t="n">
-        <v>6753742</v>
+        <v>6753749</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1370,7 +1370,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121350447</v>
+        <v>121350443</v>
       </c>
       <c r="B8" t="n">
         <v>98015</v>
@@ -1419,10 +1419,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>606565</v>
+        <v>606910</v>
       </c>
       <c r="R8" t="n">
-        <v>6753689</v>
+        <v>6753715</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1485,7 +1485,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121350449</v>
+        <v>121350441</v>
       </c>
       <c r="B9" t="n">
         <v>98015</v>
@@ -1534,10 +1534,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>606549</v>
+        <v>606974</v>
       </c>
       <c r="R9" t="n">
-        <v>6753577</v>
+        <v>6753758</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1600,7 +1600,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121350441</v>
+        <v>121350440</v>
       </c>
       <c r="B10" t="n">
         <v>98015</v>
@@ -1649,10 +1649,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>606974</v>
+        <v>606989</v>
       </c>
       <c r="R10" t="n">
-        <v>6753758</v>
+        <v>6753742</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1715,7 +1715,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121350302</v>
+        <v>121350304</v>
       </c>
       <c r="B11" t="n">
         <v>97052</v>
@@ -1750,7 +1750,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1764,10 +1764,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>606981</v>
+        <v>606420</v>
       </c>
       <c r="R11" t="n">
-        <v>6753750</v>
+        <v>6753687</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 1883-2024 artfynd.xlsx
+++ b/artfynd/A 1883-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121350447</v>
+        <v>121350443</v>
       </c>
       <c r="B2" t="n">
-        <v>98015</v>
+        <v>98021</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>606565</v>
+        <v>606910</v>
       </c>
       <c r="R2" t="n">
-        <v>6753689</v>
+        <v>6753715</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -790,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121350166</v>
+        <v>121350304</v>
       </c>
       <c r="B3" t="n">
-        <v>58183</v>
+        <v>97058</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -806,31 +806,31 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>208245</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>adult</t>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -839,10 +839,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>606558</v>
+        <v>606420</v>
       </c>
       <c r="R3" t="n">
-        <v>6753679</v>
+        <v>6753687</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -905,10 +905,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121350193</v>
+        <v>121350441</v>
       </c>
       <c r="B4" t="n">
-        <v>56566</v>
+        <v>98021</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -921,21 +921,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>219790</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -943,14 +943,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>stationär</t>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -959,10 +954,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>606479</v>
+        <v>606974</v>
       </c>
       <c r="R4" t="n">
-        <v>6753729</v>
+        <v>6753758</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1025,10 +1020,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121350302</v>
+        <v>121350193</v>
       </c>
       <c r="B5" t="n">
-        <v>97052</v>
+        <v>56567</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1041,31 +1036,36 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>dm²</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>stationär</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1074,10 +1074,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>606981</v>
+        <v>606479</v>
       </c>
       <c r="R5" t="n">
-        <v>6753750</v>
+        <v>6753729</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1140,10 +1140,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121350449</v>
+        <v>121350302</v>
       </c>
       <c r="B6" t="n">
-        <v>98015</v>
+        <v>97058</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1156,31 +1156,31 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219790</v>
+        <v>221945</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1189,10 +1189,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>606549</v>
+        <v>606981</v>
       </c>
       <c r="R6" t="n">
-        <v>6753577</v>
+        <v>6753750</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1255,10 +1255,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121350445</v>
+        <v>121350447</v>
       </c>
       <c r="B7" t="n">
-        <v>98015</v>
+        <v>98021</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1304,10 +1304,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>606512</v>
+        <v>606565</v>
       </c>
       <c r="R7" t="n">
-        <v>6753749</v>
+        <v>6753689</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1370,10 +1370,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121350443</v>
+        <v>121350445</v>
       </c>
       <c r="B8" t="n">
-        <v>98015</v>
+        <v>98021</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1419,10 +1419,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>606910</v>
+        <v>606512</v>
       </c>
       <c r="R8" t="n">
-        <v>6753715</v>
+        <v>6753749</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1485,10 +1485,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121350441</v>
+        <v>121350166</v>
       </c>
       <c r="B9" t="n">
-        <v>98015</v>
+        <v>58184</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1501,21 +1501,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219790</v>
+        <v>208245</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1523,9 +1523,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>adult</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1534,10 +1534,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>606974</v>
+        <v>606558</v>
       </c>
       <c r="R9" t="n">
-        <v>6753758</v>
+        <v>6753679</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1600,10 +1600,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121350440</v>
+        <v>121350449</v>
       </c>
       <c r="B10" t="n">
-        <v>98015</v>
+        <v>98021</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1649,10 +1649,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>606989</v>
+        <v>606549</v>
       </c>
       <c r="R10" t="n">
-        <v>6753742</v>
+        <v>6753577</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1715,10 +1715,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121350304</v>
+        <v>121350440</v>
       </c>
       <c r="B11" t="n">
-        <v>97052</v>
+        <v>98021</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1731,31 +1731,31 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221945</v>
+        <v>219790</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1764,10 +1764,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>606420</v>
+        <v>606989</v>
       </c>
       <c r="R11" t="n">
-        <v>6753687</v>
+        <v>6753742</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 1883-2024 artfynd.xlsx
+++ b/artfynd/A 1883-2024 artfynd.xlsx
@@ -1485,10 +1485,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121350166</v>
+        <v>121350449</v>
       </c>
       <c r="B9" t="n">
-        <v>58184</v>
+        <v>98021</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1501,21 +1501,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>208245</v>
+        <v>219790</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1523,9 +1523,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>adult</t>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1534,10 +1534,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>606558</v>
+        <v>606549</v>
       </c>
       <c r="R9" t="n">
-        <v>6753679</v>
+        <v>6753577</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1600,10 +1600,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121350449</v>
+        <v>121350166</v>
       </c>
       <c r="B10" t="n">
-        <v>98021</v>
+        <v>58184</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1616,21 +1616,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219790</v>
+        <v>208245</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1638,9 +1638,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>adult</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1649,10 +1649,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>606549</v>
+        <v>606558</v>
       </c>
       <c r="R10" t="n">
-        <v>6753577</v>
+        <v>6753679</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>

--- a/artfynd/A 1883-2024 artfynd.xlsx
+++ b/artfynd/A 1883-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121350443</v>
+        <v>121350441</v>
       </c>
       <c r="B2" t="n">
-        <v>98021</v>
+        <v>98022</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>606910</v>
+        <v>606974</v>
       </c>
       <c r="R2" t="n">
-        <v>6753715</v>
+        <v>6753758</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -790,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121350304</v>
+        <v>121350443</v>
       </c>
       <c r="B3" t="n">
-        <v>97058</v>
+        <v>98022</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -806,31 +806,31 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>219790</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -839,10 +839,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>606420</v>
+        <v>606910</v>
       </c>
       <c r="R3" t="n">
-        <v>6753687</v>
+        <v>6753715</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -905,10 +905,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121350441</v>
+        <v>121350445</v>
       </c>
       <c r="B4" t="n">
-        <v>98021</v>
+        <v>98022</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>606974</v>
+        <v>606512</v>
       </c>
       <c r="R4" t="n">
-        <v>6753758</v>
+        <v>6753749</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1020,10 +1020,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121350193</v>
+        <v>121350449</v>
       </c>
       <c r="B5" t="n">
-        <v>56567</v>
+        <v>98022</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1036,21 +1036,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>219790</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1058,14 +1058,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>stationär</t>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1074,10 +1069,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>606479</v>
+        <v>606549</v>
       </c>
       <c r="R5" t="n">
-        <v>6753729</v>
+        <v>6753577</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1140,10 +1135,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121350302</v>
+        <v>121350193</v>
       </c>
       <c r="B6" t="n">
-        <v>97058</v>
+        <v>56568</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1156,31 +1151,36 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221945</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>dm²</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>stationär</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1189,10 +1189,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>606981</v>
+        <v>606479</v>
       </c>
       <c r="R6" t="n">
-        <v>6753750</v>
+        <v>6753729</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1255,10 +1255,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121350447</v>
+        <v>121350166</v>
       </c>
       <c r="B7" t="n">
-        <v>98021</v>
+        <v>58185</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1271,21 +1271,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219790</v>
+        <v>208245</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1293,9 +1293,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>adult</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1304,10 +1304,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>606565</v>
+        <v>606558</v>
       </c>
       <c r="R7" t="n">
-        <v>6753689</v>
+        <v>6753679</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1370,10 +1370,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121350445</v>
+        <v>121350440</v>
       </c>
       <c r="B8" t="n">
-        <v>98021</v>
+        <v>98022</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1419,10 +1419,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>606512</v>
+        <v>606989</v>
       </c>
       <c r="R8" t="n">
-        <v>6753749</v>
+        <v>6753742</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1485,10 +1485,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121350449</v>
+        <v>121350447</v>
       </c>
       <c r="B9" t="n">
-        <v>98021</v>
+        <v>98022</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1534,10 +1534,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>606549</v>
+        <v>606565</v>
       </c>
       <c r="R9" t="n">
-        <v>6753577</v>
+        <v>6753689</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1600,10 +1600,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121350166</v>
+        <v>121350304</v>
       </c>
       <c r="B10" t="n">
-        <v>58184</v>
+        <v>97059</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1616,31 +1616,31 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>208245</v>
+        <v>221945</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>adult</t>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1649,10 +1649,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>606558</v>
+        <v>606420</v>
       </c>
       <c r="R10" t="n">
-        <v>6753679</v>
+        <v>6753687</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1715,10 +1715,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121350440</v>
+        <v>121350302</v>
       </c>
       <c r="B11" t="n">
-        <v>98021</v>
+        <v>97059</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1731,31 +1731,31 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219790</v>
+        <v>221945</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1764,10 +1764,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>606989</v>
+        <v>606981</v>
       </c>
       <c r="R11" t="n">
-        <v>6753742</v>
+        <v>6753750</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 1883-2024 artfynd.xlsx
+++ b/artfynd/A 1883-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121350441</v>
+        <v>121350302</v>
       </c>
       <c r="B2" t="n">
-        <v>98022</v>
+        <v>97059</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,31 +691,31 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219790</v>
+        <v>221945</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>606974</v>
+        <v>606981</v>
       </c>
       <c r="R2" t="n">
-        <v>6753758</v>
+        <v>6753750</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -790,7 +790,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121350443</v>
+        <v>121350447</v>
       </c>
       <c r="B3" t="n">
         <v>98022</v>
@@ -839,10 +839,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>606910</v>
+        <v>606565</v>
       </c>
       <c r="R3" t="n">
-        <v>6753715</v>
+        <v>6753689</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -905,7 +905,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121350445</v>
+        <v>121350449</v>
       </c>
       <c r="B4" t="n">
         <v>98022</v>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>606512</v>
+        <v>606549</v>
       </c>
       <c r="R4" t="n">
-        <v>6753749</v>
+        <v>6753577</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1020,10 +1020,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121350449</v>
+        <v>121350193</v>
       </c>
       <c r="B5" t="n">
-        <v>98022</v>
+        <v>56568</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1036,21 +1036,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219790</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1058,9 +1058,14 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>stationär</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1069,10 +1074,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>606549</v>
+        <v>606479</v>
       </c>
       <c r="R5" t="n">
-        <v>6753577</v>
+        <v>6753729</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1135,10 +1140,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121350193</v>
+        <v>121350445</v>
       </c>
       <c r="B6" t="n">
-        <v>56568</v>
+        <v>98022</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1151,21 +1156,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>219790</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1173,14 +1178,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>stationär</t>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1189,10 +1189,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>606479</v>
+        <v>606512</v>
       </c>
       <c r="R6" t="n">
-        <v>6753729</v>
+        <v>6753749</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1255,10 +1255,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121350166</v>
+        <v>121350304</v>
       </c>
       <c r="B7" t="n">
-        <v>58185</v>
+        <v>97059</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1271,31 +1271,31 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>208245</v>
+        <v>221945</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>adult</t>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1304,10 +1304,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>606558</v>
+        <v>606420</v>
       </c>
       <c r="R7" t="n">
-        <v>6753679</v>
+        <v>6753687</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1370,7 +1370,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121350440</v>
+        <v>121350441</v>
       </c>
       <c r="B8" t="n">
         <v>98022</v>
@@ -1419,10 +1419,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>606989</v>
+        <v>606974</v>
       </c>
       <c r="R8" t="n">
-        <v>6753742</v>
+        <v>6753758</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1485,7 +1485,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121350447</v>
+        <v>121350440</v>
       </c>
       <c r="B9" t="n">
         <v>98022</v>
@@ -1534,10 +1534,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>606565</v>
+        <v>606989</v>
       </c>
       <c r="R9" t="n">
-        <v>6753689</v>
+        <v>6753742</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1600,10 +1600,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121350304</v>
+        <v>121350443</v>
       </c>
       <c r="B10" t="n">
-        <v>97059</v>
+        <v>98022</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1616,31 +1616,31 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221945</v>
+        <v>219790</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1649,10 +1649,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>606420</v>
+        <v>606910</v>
       </c>
       <c r="R10" t="n">
-        <v>6753687</v>
+        <v>6753715</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1715,10 +1715,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121350302</v>
+        <v>121350166</v>
       </c>
       <c r="B11" t="n">
-        <v>97059</v>
+        <v>58185</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1731,31 +1731,31 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221945</v>
+        <v>208245</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>dm²</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>adult</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1764,10 +1764,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>606981</v>
+        <v>606558</v>
       </c>
       <c r="R11" t="n">
-        <v>6753750</v>
+        <v>6753679</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 1883-2024 artfynd.xlsx
+++ b/artfynd/A 1883-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121350302</v>
+        <v>121350443</v>
       </c>
       <c r="B2" t="n">
-        <v>97059</v>
+        <v>98022</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,31 +691,31 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>219790</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>606981</v>
+        <v>606910</v>
       </c>
       <c r="R2" t="n">
-        <v>6753750</v>
+        <v>6753715</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -790,7 +790,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121350447</v>
+        <v>121350440</v>
       </c>
       <c r="B3" t="n">
         <v>98022</v>
@@ -839,10 +839,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>606565</v>
+        <v>606989</v>
       </c>
       <c r="R3" t="n">
-        <v>6753689</v>
+        <v>6753742</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -905,10 +905,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121350449</v>
+        <v>121350304</v>
       </c>
       <c r="B4" t="n">
-        <v>98022</v>
+        <v>97059</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -921,31 +921,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219790</v>
+        <v>221945</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>606549</v>
+        <v>606420</v>
       </c>
       <c r="R4" t="n">
-        <v>6753577</v>
+        <v>6753687</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1020,10 +1020,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121350193</v>
+        <v>121350302</v>
       </c>
       <c r="B5" t="n">
-        <v>56568</v>
+        <v>97059</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1036,36 +1036,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>stationär</t>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1074,10 +1069,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>606479</v>
+        <v>606981</v>
       </c>
       <c r="R5" t="n">
-        <v>6753729</v>
+        <v>6753750</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1255,10 +1250,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121350304</v>
+        <v>121350193</v>
       </c>
       <c r="B7" t="n">
-        <v>97059</v>
+        <v>56568</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1271,31 +1266,36 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221945</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>dm²</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>stationär</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1304,10 +1304,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>606420</v>
+        <v>606479</v>
       </c>
       <c r="R7" t="n">
-        <v>6753687</v>
+        <v>6753729</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1485,7 +1485,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121350440</v>
+        <v>121350447</v>
       </c>
       <c r="B9" t="n">
         <v>98022</v>
@@ -1534,10 +1534,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>606989</v>
+        <v>606565</v>
       </c>
       <c r="R9" t="n">
-        <v>6753742</v>
+        <v>6753689</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1600,7 +1600,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121350443</v>
+        <v>121350449</v>
       </c>
       <c r="B10" t="n">
         <v>98022</v>
@@ -1649,10 +1649,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>606910</v>
+        <v>606549</v>
       </c>
       <c r="R10" t="n">
-        <v>6753715</v>
+        <v>6753577</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>

--- a/artfynd/A 1883-2024 artfynd.xlsx
+++ b/artfynd/A 1883-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121350443</v>
+        <v>121350166</v>
       </c>
       <c r="B2" t="n">
-        <v>98022</v>
+        <v>58185</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219790</v>
+        <v>208245</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -713,9 +713,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>adult</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>606910</v>
+        <v>606558</v>
       </c>
       <c r="R2" t="n">
-        <v>6753715</v>
+        <v>6753679</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -790,7 +790,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121350440</v>
+        <v>121350443</v>
       </c>
       <c r="B3" t="n">
         <v>98022</v>
@@ -839,10 +839,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>606989</v>
+        <v>606910</v>
       </c>
       <c r="R3" t="n">
-        <v>6753742</v>
+        <v>6753715</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -905,10 +905,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121350304</v>
+        <v>121350449</v>
       </c>
       <c r="B4" t="n">
-        <v>97059</v>
+        <v>98022</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -921,31 +921,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>219790</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>606420</v>
+        <v>606549</v>
       </c>
       <c r="R4" t="n">
-        <v>6753687</v>
+        <v>6753577</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1020,10 +1020,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121350302</v>
+        <v>121350193</v>
       </c>
       <c r="B5" t="n">
-        <v>97059</v>
+        <v>56568</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1036,31 +1036,36 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>dm²</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>stationär</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1069,10 +1074,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>606981</v>
+        <v>606479</v>
       </c>
       <c r="R5" t="n">
-        <v>6753750</v>
+        <v>6753729</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1135,10 +1140,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121350445</v>
+        <v>121350304</v>
       </c>
       <c r="B6" t="n">
-        <v>98022</v>
+        <v>97059</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1151,31 +1156,31 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219790</v>
+        <v>221945</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1184,10 +1189,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>606512</v>
+        <v>606420</v>
       </c>
       <c r="R6" t="n">
-        <v>6753749</v>
+        <v>6753687</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1250,10 +1255,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121350193</v>
+        <v>121350302</v>
       </c>
       <c r="B7" t="n">
-        <v>56568</v>
+        <v>97059</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1266,36 +1271,31 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100138</v>
+        <v>221945</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>stationär</t>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1304,10 +1304,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>606479</v>
+        <v>606981</v>
       </c>
       <c r="R7" t="n">
-        <v>6753729</v>
+        <v>6753750</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1370,7 +1370,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121350441</v>
+        <v>121350440</v>
       </c>
       <c r="B8" t="n">
         <v>98022</v>
@@ -1419,10 +1419,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>606974</v>
+        <v>606989</v>
       </c>
       <c r="R8" t="n">
-        <v>6753758</v>
+        <v>6753742</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1600,7 +1600,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121350449</v>
+        <v>121350445</v>
       </c>
       <c r="B10" t="n">
         <v>98022</v>
@@ -1649,10 +1649,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>606549</v>
+        <v>606512</v>
       </c>
       <c r="R10" t="n">
-        <v>6753577</v>
+        <v>6753749</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1715,10 +1715,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121350166</v>
+        <v>121350441</v>
       </c>
       <c r="B11" t="n">
-        <v>58185</v>
+        <v>98022</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1731,21 +1731,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>208245</v>
+        <v>219790</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1753,9 +1753,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>adult</t>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1764,10 +1764,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>606558</v>
+        <v>606974</v>
       </c>
       <c r="R11" t="n">
-        <v>6753679</v>
+        <v>6753758</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 1883-2024 artfynd.xlsx
+++ b/artfynd/A 1883-2024 artfynd.xlsx
@@ -1020,10 +1020,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121350193</v>
+        <v>121350304</v>
       </c>
       <c r="B5" t="n">
-        <v>56568</v>
+        <v>97059</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1036,36 +1036,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>stationär</t>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1074,10 +1069,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>606479</v>
+        <v>606420</v>
       </c>
       <c r="R5" t="n">
-        <v>6753729</v>
+        <v>6753687</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1140,10 +1135,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121350304</v>
+        <v>121350193</v>
       </c>
       <c r="B6" t="n">
-        <v>97059</v>
+        <v>56568</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1156,31 +1151,36 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221945</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>dm²</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>stationär</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1189,10 +1189,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>606420</v>
+        <v>606479</v>
       </c>
       <c r="R6" t="n">
-        <v>6753687</v>
+        <v>6753729</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 1883-2024 artfynd.xlsx
+++ b/artfynd/A 1883-2024 artfynd.xlsx
@@ -1020,10 +1020,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121350304</v>
+        <v>121350193</v>
       </c>
       <c r="B5" t="n">
-        <v>97059</v>
+        <v>56568</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1036,31 +1036,36 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>dm²</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>stationär</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1069,10 +1074,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>606420</v>
+        <v>606479</v>
       </c>
       <c r="R5" t="n">
-        <v>6753687</v>
+        <v>6753729</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1135,10 +1140,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121350193</v>
+        <v>121350304</v>
       </c>
       <c r="B6" t="n">
-        <v>56568</v>
+        <v>97059</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1151,36 +1156,31 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>221945</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>stationär</t>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1189,10 +1189,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>606479</v>
+        <v>606420</v>
       </c>
       <c r="R6" t="n">
-        <v>6753729</v>
+        <v>6753687</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 1883-2024 artfynd.xlsx
+++ b/artfynd/A 1883-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121350166</v>
+        <v>121350447</v>
       </c>
       <c r="B2" t="n">
-        <v>58185</v>
+        <v>98030</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>208245</v>
+        <v>219790</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -713,9 +713,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>adult</t>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>606558</v>
+        <v>606565</v>
       </c>
       <c r="R2" t="n">
-        <v>6753679</v>
+        <v>6753689</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -793,7 +793,7 @@
         <v>121350443</v>
       </c>
       <c r="B3" t="n">
-        <v>98022</v>
+        <v>98030</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -905,10 +905,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121350449</v>
+        <v>121350445</v>
       </c>
       <c r="B4" t="n">
-        <v>98022</v>
+        <v>98030</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>606549</v>
+        <v>606512</v>
       </c>
       <c r="R4" t="n">
-        <v>6753577</v>
+        <v>6753749</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1020,10 +1020,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121350193</v>
+        <v>121350166</v>
       </c>
       <c r="B5" t="n">
-        <v>56568</v>
+        <v>58188</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1036,21 +1036,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>208245</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1058,14 +1058,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>stationär</t>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>adult</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1074,10 +1069,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>606479</v>
+        <v>606558</v>
       </c>
       <c r="R5" t="n">
-        <v>6753729</v>
+        <v>6753679</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1140,10 +1135,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121350304</v>
+        <v>121350440</v>
       </c>
       <c r="B6" t="n">
-        <v>97059</v>
+        <v>98030</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1156,31 +1151,31 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221945</v>
+        <v>219790</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1189,10 +1184,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>606420</v>
+        <v>606989</v>
       </c>
       <c r="R6" t="n">
-        <v>6753687</v>
+        <v>6753742</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1255,10 +1250,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121350302</v>
+        <v>121350449</v>
       </c>
       <c r="B7" t="n">
-        <v>97059</v>
+        <v>98030</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1271,31 +1266,31 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221945</v>
+        <v>219790</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1304,10 +1299,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>606981</v>
+        <v>606549</v>
       </c>
       <c r="R7" t="n">
-        <v>6753750</v>
+        <v>6753577</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1370,10 +1365,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121350440</v>
+        <v>121350441</v>
       </c>
       <c r="B8" t="n">
-        <v>98022</v>
+        <v>98030</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1419,10 +1414,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>606989</v>
+        <v>606974</v>
       </c>
       <c r="R8" t="n">
-        <v>6753742</v>
+        <v>6753758</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1485,10 +1480,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121350447</v>
+        <v>121350193</v>
       </c>
       <c r="B9" t="n">
-        <v>98022</v>
+        <v>56569</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1501,21 +1496,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219790</v>
+        <v>100138</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1523,9 +1518,14 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>stationär</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1534,10 +1534,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>606565</v>
+        <v>606479</v>
       </c>
       <c r="R9" t="n">
-        <v>6753689</v>
+        <v>6753729</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1600,10 +1600,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121350445</v>
+        <v>121350302</v>
       </c>
       <c r="B10" t="n">
-        <v>98022</v>
+        <v>97067</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1616,31 +1616,31 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219790</v>
+        <v>221945</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1649,10 +1649,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>606512</v>
+        <v>606981</v>
       </c>
       <c r="R10" t="n">
-        <v>6753749</v>
+        <v>6753750</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1715,10 +1715,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121350441</v>
+        <v>121350304</v>
       </c>
       <c r="B11" t="n">
-        <v>98022</v>
+        <v>97067</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1731,31 +1731,31 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219790</v>
+        <v>221945</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1764,10 +1764,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>606974</v>
+        <v>606420</v>
       </c>
       <c r="R11" t="n">
-        <v>6753758</v>
+        <v>6753687</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
